--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2032-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2032-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB8D05B8-CA78-4041-8C05-FA24527E37E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A58122C-F39C-4840-836B-4F4A3E1AC0B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{4F8B3999-5389-45CF-9E11-2AEDB4C78719}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{C450610E-7CD2-4D04-B5BC-88A718839C69}"/>
   </bookViews>
   <sheets>
     <sheet name="2032-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1598,29 +1598,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ACE027-72E2-438F-AFAC-450F98635D6D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{621B3AAC-838F-46C9-910E-1A4A70FBD193}">
   <dimension ref="A1:X49"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1654,7 +1653,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1690,7 +1689,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1742,7 +1741,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1810,7 +1809,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1882,7 +1881,7 @@
         <v>3.11</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1954,7 +1953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -2026,7 +2025,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2098,7 +2097,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2170,7 +2169,7 @@
         <v>4.38</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2019</v>
       </c>
@@ -2242,7 +2241,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2018</v>
       </c>
@@ -2314,7 +2313,7 @@
         <v>1.62</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2017</v>
       </c>
@@ -2386,7 +2385,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2016</v>
       </c>
@@ -2458,7 +2457,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2015</v>
       </c>
@@ -2530,7 +2529,7 @@
         <v>2.67</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2014</v>
       </c>
@@ -2602,7 +2601,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2013</v>
       </c>
@@ -2674,7 +2673,7 @@
         <v>7.35</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2012</v>
       </c>
@@ -2746,7 +2745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2011</v>
       </c>
@@ -2818,7 +2817,7 @@
         <v>2.17</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="41">
         <v>2010</v>
       </c>
@@ -2890,7 +2889,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="43"/>
       <c r="B20" s="44"/>
       <c r="C20" s="18" t="s">
@@ -2918,7 +2917,7 @@
       <c r="W20" s="50"/>
       <c r="X20" s="46"/>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="39">
         <v>2009</v>
       </c>
@@ -2990,7 +2989,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2008</v>
       </c>
@@ -3062,7 +3061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="39">
         <v>2007</v>
       </c>
@@ -3134,7 +3133,7 @@
         <v>8.32</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="41">
         <v>2006</v>
       </c>
@@ -3206,7 +3205,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="43"/>
       <c r="B25" s="44"/>
       <c r="C25" s="18" t="s">
@@ -3234,7 +3233,7 @@
       <c r="W25" s="50"/>
       <c r="X25" s="46"/>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <v>2005</v>
       </c>
@@ -3306,7 +3305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="41">
         <v>2004</v>
       </c>
@@ -3378,7 +3377,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="43"/>
       <c r="B28" s="44"/>
       <c r="C28" s="18" t="s">
@@ -3406,7 +3405,7 @@
       <c r="W28" s="50"/>
       <c r="X28" s="46"/>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="53">
         <v>2003</v>
       </c>
@@ -3478,7 +3477,7 @@
         <v>7.69</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="55"/>
       <c r="B30" s="56"/>
       <c r="C30" s="20" t="s">
@@ -3506,7 +3505,7 @@
       <c r="W30" s="62"/>
       <c r="X30" s="58"/>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="41">
         <v>2002</v>
       </c>
@@ -3578,7 +3577,7 @@
         <v>8.36</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="43"/>
       <c r="B32" s="44"/>
       <c r="C32" s="18" t="s">
@@ -3606,7 +3605,7 @@
       <c r="W32" s="50"/>
       <c r="X32" s="46"/>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="53">
         <v>2001</v>
       </c>
@@ -3678,7 +3677,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="55"/>
       <c r="B34" s="56"/>
       <c r="C34" s="20" t="s">
@@ -3706,7 +3705,7 @@
       <c r="W34" s="62"/>
       <c r="X34" s="58"/>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="41">
         <v>2000</v>
       </c>
@@ -3778,7 +3777,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="43"/>
       <c r="B36" s="44"/>
       <c r="C36" s="18" t="s">
@@ -3806,7 +3805,7 @@
       <c r="W36" s="50"/>
       <c r="X36" s="46"/>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="53">
         <v>1999</v>
       </c>
@@ -3878,7 +3877,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="55"/>
       <c r="B38" s="56"/>
       <c r="C38" s="20" t="s">
@@ -3906,7 +3905,7 @@
       <c r="W38" s="62"/>
       <c r="X38" s="58"/>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>1998</v>
       </c>
@@ -3978,7 +3977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="39">
         <v>1997</v>
       </c>
@@ -4050,7 +4049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="37">
         <v>1996</v>
       </c>
@@ -4122,7 +4121,7 @@
         <v>1.94</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="53">
         <v>1995</v>
       </c>
@@ -4194,7 +4193,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="55"/>
       <c r="B43" s="56"/>
       <c r="C43" s="20" t="s">
@@ -4222,7 +4221,7 @@
       <c r="W43" s="62"/>
       <c r="X43" s="58"/>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="41">
         <v>1994</v>
       </c>
@@ -4294,7 +4293,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="43"/>
       <c r="B45" s="44"/>
       <c r="C45" s="18" t="s">
@@ -4322,7 +4321,7 @@
       <c r="W45" s="50"/>
       <c r="X45" s="46"/>
     </row>
-    <row r="46" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="53">
         <v>1993</v>
       </c>
@@ -4394,7 +4393,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="55"/>
       <c r="B47" s="56"/>
       <c r="C47" s="20" t="s">
@@ -4422,7 +4421,7 @@
       <c r="W47" s="62"/>
       <c r="X47" s="58"/>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="37">
         <v>1992</v>
       </c>
@@ -4494,7 +4493,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="39" t="s">
         <v>66</v>
       </c>
